--- a/Result/profitability/1453.xlsx
+++ b/Result/profitability/1453.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08499999999999999</v>
+        <v>0.1775</v>
       </c>
       <c r="N2" t="n">
-        <v>331.29375</v>
+        <v>331.36875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0.13625</v>
+        <v>0.2225</v>
       </c>
       <c r="N3" t="n">
-        <v>327.225</v>
+        <v>156.515</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09875</v>
+        <v>0.1875</v>
       </c>
       <c r="N4" t="n">
-        <v>151.535</v>
+        <v>151.3375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07750000000000001</v>
+        <v>-0.005000000000000032</v>
       </c>
       <c r="N5" t="n">
-        <v>138.21125</v>
+        <v>139.70875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05875000000000001</v>
+        <v>-0.003750000000000024</v>
       </c>
       <c r="N6" t="n">
-        <v>134.96625</v>
+        <v>135.0325</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1025</v>
+        <v>-0.02750000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>128.24625</v>
+        <v>21.30125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.10625</v>
+        <v>-0.02625000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>14.16875</v>
+        <v>13.33875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.83</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003749999999999989</v>
+        <v>0.003749999999999976</v>
       </c>
       <c r="N9" t="n">
         <v>10.33875</v>
@@ -1648,7 +1648,7 @@
         <v>-0.1225</v>
       </c>
       <c r="N10" t="n">
-        <v>7.673749999999999</v>
+        <v>7.67375</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.1625</v>
       </c>
       <c r="N11" t="n">
-        <v>6.092499999999999</v>
+        <v>6.0925</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.35</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06875000000000001</v>
+        <v>-0.06875000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>5.295</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2580.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>77</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67</v>
+      </c>
+      <c r="K75" t="n">
+        <v>67</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N75" t="n">
+        <v>334.33375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.640000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1038636008133896</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2644007945265945</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
